--- a/MainTop/23.12.2025 имена/23.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/23.12.2025 имена/23.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5D0FED-FF1C-4988-92D2-6B8B7DFE7129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD0AF85-72EF-44FC-9DA0-5829ADB73B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>штрихкод</t>
   </si>
   <si>
-    <t>количество</t>
-  </si>
-  <si>
     <t>Термобирки Максим</t>
   </si>
   <si>
@@ -317,6 +314,9 @@
   </si>
   <si>
     <t>OZN1296068698</t>
+  </si>
+  <si>
+    <t>Num_Copies</t>
   </si>
 </sst>
 </file>
@@ -720,6 +720,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -729,15 +733,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -745,10 +749,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -756,10 +760,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -767,10 +771,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -778,10 +782,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -789,10 +793,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -800,10 +804,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -811,10 +815,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -822,10 +826,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -833,10 +837,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -844,10 +848,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -855,10 +859,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -866,10 +870,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -877,10 +881,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -888,10 +892,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -899,10 +903,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -910,10 +914,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -921,10 +925,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -932,10 +936,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -943,10 +947,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -954,10 +958,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -965,10 +969,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -976,10 +980,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -987,10 +991,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -998,10 +1002,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1009,10 +1013,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1020,10 +1024,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1031,10 +1035,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -1042,10 +1046,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1053,10 +1057,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -1064,10 +1068,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1075,10 +1079,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1086,10 +1090,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1097,10 +1101,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1108,10 +1112,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1130,10 +1134,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1141,10 +1145,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1152,10 +1156,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1163,10 +1167,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1174,10 +1178,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1196,10 +1200,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1207,10 +1211,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1218,10 +1222,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1229,10 +1233,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1240,10 +1244,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1251,10 +1255,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C49">
         <v>2</v>

--- a/MainTop/23.12.2025 имена/23.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/23.12.2025 имена/23.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\23.12.2025 имена\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\23.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD0AF85-72EF-44FC-9DA0-5829ADB73B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F94511-672C-4B04-979B-941DB9136BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,11 +375,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -737,534 +738,535 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>